--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488085_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488085_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6303</v>
+        <v>1.7059</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4432</v>
+        <v>5.2208</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.8129</v>
+        <v>-3.5148</v>
       </c>
       <c r="G2" t="n">
         <v>-1.5344</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9179</v>
+        <v>-0.0065</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1235</v>
+        <v>-0.0989</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7944</v>
+        <v>0.0925</v>
       </c>
       <c r="V2" t="n">
         <v>1.0663</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.8333</v>
+        <v>-2.5911</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1903</v>
+        <v>-0.0885</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.643</v>
+        <v>-2.5026</v>
       </c>
       <c r="G5" t="n">
         <v>-2.5485</v>
@@ -844,13 +844,13 @@
         <v>0.5947</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0957</v>
+        <v>-0.8535</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.301</v>
+        <v>-0.1991</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7948</v>
+        <v>-0.6544</v>
       </c>
       <c r="V5" t="n">
         <v>0.2163</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.845</v>
+        <v>-3.2534</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3875</v>
+        <v>-0.9363</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4575</v>
+        <v>-2.3171</v>
       </c>
       <c r="G6" t="n">
         <v>-4.0011</v>
@@ -922,13 +922,13 @@
         <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8389</v>
+        <v>0.4305</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8811</v>
+        <v>0.3323</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0422</v>
+        <v>0.0982</v>
       </c>
       <c r="V6" t="n">
         <v>-0.674</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.2947</v>
+        <v>-3.7406</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2731</v>
+        <v>-0.8032</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0216</v>
+        <v>-2.9373</v>
       </c>
       <c r="G7" t="n">
         <v>-3.8718</v>
@@ -1000,13 +1000,13 @@
         <v>1.1893</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2249</v>
+        <v>-0.6708</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6019</v>
+        <v>-0.132</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.623</v>
+        <v>-0.5387</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3873</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.7452</v>
+        <v>-4.5728</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6713</v>
+        <v>-3.1619</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0739</v>
+        <v>-1.4108</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7616000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3883</v>
+        <v>0.5607</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4661</v>
+        <v>0.0433</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8544</v>
+        <v>0.5174</v>
       </c>
       <c r="V8" t="n">
         <v>-0.4074</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.028</v>
+        <v>-5.5934</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8185</v>
+        <v>-0.5524</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.2095</v>
+        <v>-5.041</v>
       </c>
       <c r="G9" t="n">
         <v>-3.6282</v>
@@ -1156,13 +1156,13 @@
         <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7965</v>
+        <v>-1.3619</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8515</v>
+        <v>-0.5854</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.945</v>
+        <v>-0.7765</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5944</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.792999999999999</v>
+        <v>-8.748200000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3157</v>
+        <v>-4.3552</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.4773</v>
+        <v>-4.393</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8468</v>
@@ -1234,13 +1234,13 @@
         <v>2.1805</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5678</v>
+        <v>-0.5231</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2237</v>
+        <v>-0.2632</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3441</v>
+        <v>-0.2598</v>
       </c>
       <c r="V10" t="n">
         <v>-3.4051</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.065300000000001</v>
+        <v>-8.833399999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7179</v>
+        <v>-5.5142</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3474</v>
+        <v>-3.3193</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5324</v>
@@ -1312,13 +1312,13 @@
         <v>2.1805</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3285</v>
+        <v>-1.0967</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9139</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4146</v>
+        <v>-0.3865</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2666</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.7302</v>
+        <v>-9.7654</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4897</v>
+        <v>-3.9179</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.2406</v>
+        <v>-5.8475</v>
       </c>
       <c r="G12" t="n">
         <v>-6.2875</v>
@@ -1390,13 +1390,13 @@
         <v>2.3787</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3221</v>
+        <v>-1.3572</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1525</v>
+        <v>-0.5807</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1696</v>
+        <v>-0.7765</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3278</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-45.6431</v>
+        <v>-45.3311</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.7559</v>
+        <v>-13.4439</v>
       </c>
       <c r="F13" t="n">
-        <v>-31.8873</v>
+        <v>-31.887</v>
       </c>
       <c r="G13" t="n">
         <v>-24.41869999999999</v>
@@ -1468,13 +1468,13 @@
         <v>14.8669</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.5244</v>
+        <v>-5.212499999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.5684</v>
+        <v>-2.2563</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.9562</v>
+        <v>-2.956</v>
       </c>
       <c r="V13" t="n">
         <v>-6.780000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.6225</v>
+        <v>14.8439</v>
       </c>
       <c r="E14" t="n">
-        <v>11.1091</v>
+        <v>11.0072</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5134</v>
+        <v>3.8366</v>
       </c>
       <c r="G14" t="n">
         <v>9.6107</v>
@@ -1546,13 +1546,13 @@
         <v>2.9733</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4944</v>
+        <v>0.7158</v>
       </c>
       <c r="T14" t="n">
-        <v>0.191</v>
+        <v>0.0891</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3034</v>
+        <v>0.6266</v>
       </c>
       <c r="V14" t="n">
         <v>1.5441</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.494199999999999</v>
+        <v>7.8779</v>
       </c>
       <c r="E15" t="n">
-        <v>4.602</v>
+        <v>5.5454</v>
       </c>
       <c r="F15" t="n">
-        <v>3.8922</v>
+        <v>2.3325</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3171</v>
+        <v>2.6555</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6885</v>
+        <v>1.5266</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6287</v>
+        <v>1.1289</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4879</v>
+        <v>3.6376</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2781</v>
+        <v>1.5808</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2098</v>
+        <v>2.0568</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1708</v>
+        <v>-0.9822</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5896</v>
+        <v>-0.0542</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4189</v>
+        <v>-0.928</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5769</v>
+        <v>2.7751</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1087</v>
+        <v>1.0242</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6227</v>
+        <v>0.4847</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4861</v>
+        <v>0.5395</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4737</v>
+        <v>2.4142</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4737</v>
+        <v>2.4142</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.0372</v>
+        <v>7.2254</v>
       </c>
       <c r="E16" t="n">
-        <v>5.9529</v>
+        <v>3.787</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0843</v>
+        <v>3.4384</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6555</v>
+        <v>3.3171</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5266</v>
+        <v>0.6885</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1289</v>
+        <v>2.6287</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6376</v>
+        <v>3.4879</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5808</v>
+        <v>1.2781</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0568</v>
+        <v>2.2098</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9822</v>
+        <v>-0.1708</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0542</v>
+        <v>-0.5896</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.928</v>
+        <v>0.4189</v>
       </c>
       <c r="P16" t="n">
-        <v>1.784</v>
+        <v>0.5947</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7751</v>
+        <v>2.5769</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1835</v>
+        <v>1.8399</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8922</v>
+        <v>0.8077</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2914</v>
+        <v>1.0322</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4142</v>
+        <v>1.4737</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4142</v>
+        <v>1.4737</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.3202</v>
+        <v>5.7358</v>
       </c>
       <c r="E17" t="n">
-        <v>4.8246</v>
+        <v>3.9078</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4956</v>
+        <v>1.828</v>
       </c>
       <c r="G17" t="n">
         <v>4.2389</v>
@@ -1780,13 +1780,13 @@
         <v>2.5769</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6582</v>
+        <v>1.0738</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6227</v>
+        <v>0.7058</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0355</v>
+        <v>0.3679</v>
       </c>
       <c r="V17" t="n">
         <v>1.8107</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.5143</v>
+        <v>5.5153</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4718</v>
+        <v>2.9812</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0424</v>
+        <v>2.5341</v>
       </c>
       <c r="G18" t="n">
         <v>3.5002</v>
@@ -1858,13 +1858,13 @@
         <v>2.9733</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3844</v>
+        <v>0.6166</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4881</v>
+        <v>0.0212</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1037</v>
+        <v>0.5954</v>
       </c>
       <c r="V18" t="n">
         <v>0.4074</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.8394</v>
+        <v>4.4891</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3429</v>
+        <v>1.4447</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4965</v>
+        <v>3.0444</v>
       </c>
       <c r="G19" t="n">
         <v>3.3545</v>
@@ -1936,13 +1936,13 @@
         <v>2.1805</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3873</v>
+        <v>0.2624</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1944</v>
+        <v>-0.0926</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1929</v>
+        <v>0.355</v>
       </c>
       <c r="V19" t="n">
         <v>0.674</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3129</v>
+        <v>2.7544</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4665</v>
+        <v>1.7721</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8464</v>
+        <v>0.9822</v>
       </c>
       <c r="G20" t="n">
         <v>0.1992</v>
@@ -2014,13 +2014,13 @@
         <v>0.3964</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5102</v>
+        <v>0.9516</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2717</v>
+        <v>0.5773</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2386</v>
+        <v>0.3744</v>
       </c>
       <c r="V20" t="n">
         <v>1.2071</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.018</v>
+        <v>1.8506</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7685</v>
+        <v>-0.2592</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7865</v>
+        <v>2.1098</v>
       </c>
       <c r="G21" t="n">
         <v>-1.197</v>
@@ -2092,13 +2092,13 @@
         <v>3.1716</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2764</v>
+        <v>0.5561</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4771</v>
+        <v>0.0322</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2007</v>
+        <v>0.5239</v>
       </c>
       <c r="V21" t="n">
         <v>3.2843</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8411999999999999</v>
+        <v>1.0462</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2665</v>
+        <v>0.3684</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5746</v>
+        <v>0.6778</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9325</v>
@@ -2170,13 +2170,13 @@
         <v>2.5769</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1373</v>
+        <v>0.3423</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1834</v>
+        <v>-0.0815</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3207</v>
+        <v>0.4239</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9405</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.3744</v>
+        <v>-0.4706</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8325</v>
+        <v>1.24</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2069</v>
+        <v>-1.7106</v>
       </c>
       <c r="G25" t="n">
         <v>0.2903</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3715</v>
+        <v>0.5323</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1762</v>
+        <v>0.2313</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1953</v>
+        <v>0.301</v>
       </c>
       <c r="V25" t="n">
         <v>-2.6808</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.1879</v>
+        <v>-3.7138</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.4186</v>
+        <v>-1.113</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.7693</v>
+        <v>-2.6008</v>
       </c>
       <c r="G26" t="n">
         <v>-1.8236</v>
@@ -2482,13 +2482,13 @@
         <v>0.1982</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1483</v>
+        <v>0.3258</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1248</v>
+        <v>0.1808</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0235</v>
+        <v>0.145</v>
       </c>
       <c r="V26" t="n">
         <v>-2.4142</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>45.64299999999999</v>
+        <v>48.3596</v>
       </c>
       <c r="E27" t="n">
-        <v>31.8871</v>
+        <v>31.887</v>
       </c>
       <c r="F27" t="n">
-        <v>13.7557</v>
+        <v>16.4724</v>
       </c>
       <c r="G27" t="n">
         <v>24.41869999999999</v>
@@ -2530,7 +2530,7 @@
         <v>0.369</v>
       </c>
       <c r="I27" t="n">
-        <v>24.0497</v>
+        <v>24.04969999999999</v>
       </c>
       <c r="J27" t="n">
         <v>32.5415</v>
@@ -2542,7 +2542,7 @@
         <v>27.24569999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>-8.122900000000001</v>
+        <v>-8.1229</v>
       </c>
       <c r="N27" t="n">
         <v>-4.9268</v>
@@ -2560,13 +2560,13 @@
         <v>23.7867</v>
       </c>
       <c r="S27" t="n">
-        <v>5.5244</v>
+        <v>8.2408</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9563</v>
+        <v>2.956</v>
       </c>
       <c r="U27" t="n">
-        <v>2.5684</v>
+        <v>5.2848</v>
       </c>
       <c r="V27" t="n">
         <v>6.78</v>
